--- a/tools/importer/reports/import-landing-page.report.xlsx
+++ b/tools/importer/reports/import-landing-page.report.xlsx
@@ -262,13 +262,13 @@
     <t>ca/en/magazine.report.json</t>
   </si>
   <si>
-    <t>["columns","secure-teasers","secure-teasers","cards"]</t>
+    <t>["columns","secure-teasers","secure-teasers","recent-articles"]</t>
   </si>
   <si>
     <t>ca/en/magazine</t>
   </si>
   <si>
-    <t>2026-09-09T19:14:25.327Z</t>
+    <t>2026-09-17T17:39:08.223Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -283,7 +283,7 @@
     <t>us/en/about-us</t>
   </si>
   <si>
-    <t>2026-09-08T20:47:50.809Z</t>
+    <t>2026-09-17T17:32:04.408Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/about-us.html</t>
@@ -319,7 +319,7 @@
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-09-09T19:14:21.177Z</t>
+    <t>2026-09-17T17:39:02.819Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine.html</t>
@@ -868,7 +868,7 @@
     <t>us/en/magazine/arctic-surfing</t>
   </si>
   <si>
-    <t>2026-09-09T16:53:54.843Z</t>
+    <t>2026-09-09T19:51:32.413Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/arctic-surfing.html</t>
@@ -880,7 +880,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-09-09T16:53:59.991Z</t>
+    <t>2026-09-09T19:51:36.344Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/guide-la-skateparks.html</t>
@@ -892,7 +892,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-09-09T16:54:04.869Z</t>
+    <t>2026-09-09T19:51:42.282Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/san-diego-surf.html</t>
@@ -904,7 +904,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-09-09T16:54:10.205Z</t>
+    <t>2026-09-09T19:51:46.067Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/ski-touring.html</t>
@@ -916,7 +916,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-09-09T16:54:15.560Z</t>
+    <t>2026-09-09T19:51:50.555Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/western-australia.html</t>
